--- a/Output/peer_comparison.xlsx
+++ b/Output/peer_comparison.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Pharmaceuticals'!$A$1:$V$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Power &amp; Utilities'!$A$1:$V$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Private Banks'!$A$1:$V$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Public Sector Banks'!$A$1:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Public Sector Banks'!$A$1:$V$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Steel'!$A$1:$V$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69,12 +69,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,6 +136,9 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -143,9 +146,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -661,358 +661,378 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd</t>
+          <t>Eicher Motors Ltd</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>26.61</v>
+        <v>24.2</v>
       </c>
       <c r="D2" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="P2" s="5" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>6486</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="3" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>66.67</v>
+      </c>
       <c r="S2" s="3" t="n">
-        <v>174.4167</v>
+        <v>114.71</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>1.1405</v>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>57.14</v>
+        <v>0.72</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>22.17</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>83.33</v>
-      </c>
+          <t>TVS Motor Company Ltd</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0.0232</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>890</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+        <v>4.54</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="S3" s="3" t="n">
-        <v>114.7059</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0.7154</v>
-      </c>
-      <c r="V3" s="5" t="n">
-        <v>28.57</v>
-      </c>
+        <v>2.91</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd</t>
+          <t>Bajaj Auto Ltd</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21.14</v>
+        <v>26.5</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>42.86</v>
+        <v>83.33</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>29.1</v>
+        <v>33.5</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.9</v>
+        <v>17.18</v>
       </c>
       <c r="H4" s="5" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>174.42</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="8" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="P5" s="9" t="n">
         <v>71.43000000000001</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>0.0342</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>3095</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="3" t="n">
-        <v>47.2685</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1.4449</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Maruti Suzuki India Ltd</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="J5" s="8" t="n">
+      <c r="Q5" s="8" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>117.91</v>
+      </c>
+      <c r="T5" s="9" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="K5" s="7" t="n">
-        <v>4936</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="6" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="7" t="n">
-        <v>117.9072</v>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>1.2303</v>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v>85.70999999999999</v>
+      <c r="U5" s="8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd</t>
+          <t>Hero MotoCorp Ltd</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.46</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F6" s="9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N6" s="6" t="n">
         <v>16.67</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1.2631</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>45133</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>16.67</v>
+      </c>
       <c r="S6" s="3" t="n">
-        <v>6.5302</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>42.86</v>
+        <v>47.27</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>57.14</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.1851</v>
+        <v>1.44</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TVS Motor Company Ltd</t>
+          <t>Tata Motors Ltd</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>26.22</v>
+        <v>49.4</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>16.67</v>
+      </c>
       <c r="G7" s="3" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>3.8334</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>-2254</v>
-      </c>
-      <c r="L7" s="5" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>28.57</v>
       </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="O7" s="3" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>42.86</v>
+      </c>
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>2.9077</v>
-      </c>
-      <c r="T7" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0.9315</v>
-      </c>
-      <c r="V7" s="5" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="T7" s="4" t="n">
         <v>42.86</v>
       </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1026,52 +1046,60 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>28.57</v>
+        <v>17.99</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>33.33</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>26.98</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>8.82</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>42.86</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.6414</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>-11245</v>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
+        <v>1.64</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>83.33</v>
+      </c>
       <c r="S8" s="3" t="n">
-        <v>3.7647</v>
-      </c>
-      <c r="T8" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T8" s="4" t="n">
         <v>28.57</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.5925</v>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v>14.29</v>
+        <v>0.59</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9"/>
@@ -1083,10 +1111,10 @@
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="n">
-        <v>22.17</v>
+        <v>23.1</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>57.14</v>
+        <v>58.34</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>28.04</v>
@@ -1101,23 +1129,31 @@
         <v>57.14</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>3095</v>
-      </c>
-      <c r="L10" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="11" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="P10" s="11" t="n">
         <v>57.14</v>
       </c>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="10" t="n"/>
-      <c r="R10" s="10" t="n"/>
+      <c r="Q10" s="11" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="R10" s="11" t="n">
+        <v>58.34</v>
+      </c>
       <c r="S10" s="11" t="n">
         <v>47.27</v>
       </c>
@@ -1128,7 +1164,7 @@
         <v>1.14</v>
       </c>
       <c r="V10" s="11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1144,12 +1180,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -1295,52 +1331,60 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>16.72</v>
+        <v>17.9</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>6.63</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>13.94</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T2" s="4" t="n">
         <v>66.67</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>14.8674</v>
-      </c>
-      <c r="J2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>13296</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="3" t="n">
-        <v>1.6107</v>
-      </c>
-      <c r="T2" s="5" t="n">
+      <c r="U2" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V2" s="4" t="n">
         <v>50</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>66.67</v>
       </c>
     </row>
     <row r="3">
@@ -1355,169 +1399,245 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>33.33</v>
+        <v>16.7</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>6.33</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>15.94</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>100</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>12.1437</v>
-      </c>
-      <c r="J3" s="5" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="J3" s="4" t="n">
         <v>33.33</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>-7559</v>
-      </c>
-      <c r="L3" s="5" t="n">
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>66.67</v>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.8967</v>
-      </c>
-      <c r="T3" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T3" s="5" t="n">
         <v>100</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.07149999999999999</v>
-      </c>
-      <c r="V3" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>33.33</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr"/>
+      <c r="V4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Punjab National Bank</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>61.31999999999999</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="C5" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1.63</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>PEER GROUP MEDIAN</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="J7" s="11" t="n">
         <v>33.33</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>3.6843</v>
-      </c>
-      <c r="J4" s="5" t="n">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="11" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="N7" s="11" t="n">
         <v>66.67</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>-29445</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="3" t="n">
-        <v>1.507</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="11" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="O7" s="11" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="R7" s="11" t="n">
         <v>66.67</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="S7" s="11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T7" s="11" t="n">
         <v>66.67</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>-7559</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="10" t="n"/>
-      <c r="S6" s="11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T6" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="U6" s="11" t="n">
+      <c r="U7" s="11" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V6" s="11" t="n">
-        <v>66.67</v>
+      <c r="V7" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V4"/>
+  <autoFilter ref="A1:V5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1680,51 +1800,59 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="D2" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>50</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="4" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="4" t="n">
         <v>50</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.5309</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>9789</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+        <v>0.53</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="S2" s="3" t="n">
-        <v>126.4654</v>
-      </c>
-      <c r="T2" s="4" t="n">
+        <v>126.47</v>
+      </c>
+      <c r="T2" s="5" t="n">
         <v>100</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.9360000000000001</v>
-      </c>
-      <c r="V2" s="4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="V2" s="5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1740,52 +1868,52 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="D3" s="4" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>100</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>75</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>100</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3717</v>
+        <v>0.37</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-2336</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>50</v>
-      </c>
+        <v>66.67</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="O3" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>25</v>
+      </c>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>8.0046</v>
-      </c>
-      <c r="T3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" s="5" t="n">
         <v>75</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="V3" s="9" t="n">
-        <v>25</v>
+      <c r="V3" s="4" t="n">
+        <v>33.33</v>
       </c>
     </row>
     <row r="4">
@@ -1800,113 +1928,113 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="D4" s="4" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>75</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>13.36</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>5.13</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>75</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.1328</v>
-      </c>
-      <c r="J4" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="L4" s="9" t="n">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>66.67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Tata Steel Ltd</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="3" t="n">
-        <v>3.6591</v>
-      </c>
-      <c r="T4" s="5" t="n">
+      <c r="E5" s="8" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="8" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="P5" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>0.7679</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Tata Steel Ltd</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>-5.33</v>
-      </c>
-      <c r="D5" s="8" t="n">
+      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="R5" s="7" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T5" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>0.9462</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>6048</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="6" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="7" t="n">
-        <v>2.1634</v>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>0.8509</v>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v>75</v>
-      </c>
+      <c r="U5" s="7" t="inlineStr"/>
+      <c r="V5" s="7" t="inlineStr"/>
     </row>
     <row r="6"/>
     <row r="7">
@@ -1917,7 +2045,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="n">
-        <v>10.56</v>
+        <v>10.93</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>62.5</v>
@@ -1935,23 +2063,31 @@
         <v>62.5</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>1856</v>
-      </c>
-      <c r="L7" s="11" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="11" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="P7" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="M7" s="10" t="n"/>
-      <c r="N7" s="10" t="n"/>
-      <c r="O7" s="10" t="n"/>
-      <c r="P7" s="10" t="n"/>
-      <c r="Q7" s="10" t="n"/>
-      <c r="R7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>75</v>
+      </c>
       <c r="S7" s="11" t="n">
         <v>5.83</v>
       </c>
@@ -1959,10 +2095,10 @@
         <v>62.5</v>
       </c>
       <c r="U7" s="11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="V7" s="11" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
@@ -2118,63 +2254,71 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Bajaj Finance Ltd</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="7" t="n">
+      <c r="C2" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="F2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" s="7" t="n">
+      <c r="F2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="8" t="n">
         <v>26.29</v>
       </c>
-      <c r="H2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>3.8248</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>-79931</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="M2" s="6" t="inlineStr"/>
-      <c r="N2" s="6" t="inlineStr"/>
-      <c r="O2" s="6" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="7" t="n">
-        <v>2689.1667</v>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="U2" s="7" t="n">
-        <v>0.1463</v>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v>66.67</v>
+      <c r="H2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" s="7" t="inlineStr"/>
+      <c r="L2" s="7" t="inlineStr"/>
+      <c r="M2" s="8" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="N2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="P2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="R2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>2689.17</v>
+      </c>
+      <c r="T2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="V2" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -2189,53 +2333,53 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="D3" s="5" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>33.33</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="4" t="n">
         <v>66.67</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>20.33</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="4" t="n">
         <v>66.67</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>3.994</v>
-      </c>
-      <c r="J3" s="5" t="n">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>33.33</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>-31359</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="Q3" s="3" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>33.33</v>
+      </c>
       <c r="S3" s="3" t="n">
-        <v>0.6767</v>
-      </c>
-      <c r="T3" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T3" s="4" t="n">
         <v>33.33</v>
       </c>
-      <c r="U3" s="3" t="n">
-        <v>0.1466</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>100</v>
-      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2249,52 +2393,60 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="D4" s="5" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>66.67</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>33.33</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>17.85</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="4" t="n">
         <v>33.33</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6.8634</v>
-      </c>
-      <c r="J4" s="9" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>-38538</v>
-      </c>
-      <c r="L4" s="5" t="n">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>66.67</v>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
+      <c r="Q4" s="3" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>66.67</v>
+      </c>
       <c r="S4" s="3" t="n">
-        <v>21.2118</v>
-      </c>
-      <c r="T4" s="5" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="T4" s="4" t="n">
         <v>66.67</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.1223</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>33.33</v>
+        <v>0.12</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5"/>
@@ -2306,7 +2458,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="11" t="n">
-        <v>17.46</v>
+        <v>20.2</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>66.67</v>
@@ -2324,23 +2476,31 @@
         <v>66.67</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>3.99</v>
+        <v>5.34</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>-38538</v>
-      </c>
-      <c r="L6" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="11" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="N6" s="11" t="n">
         <v>66.67</v>
       </c>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="10" t="n"/>
+      <c r="O6" s="11" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Q6" s="11" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="R6" s="11" t="n">
+        <v>66.67</v>
+      </c>
       <c r="S6" s="11" t="n">
         <v>21.21</v>
       </c>
@@ -2348,10 +2508,10 @@
         <v>66.67</v>
       </c>
       <c r="U6" s="11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V6" s="11" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2509,361 +2669,401 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ITC Ltd</t>
+          <t>Nestle India Ltd</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>27.85</v>
+        <v>135.61</v>
       </c>
       <c r="D2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>185.43</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>71.43000000000001</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="I2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="T2" s="4" t="n">
         <v>71.43000000000001</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>29.28</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>18742</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="3" t="n">
-        <v>362.9625</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>100</v>
-      </c>
       <c r="U2" s="3" t="n">
-        <v>0.7723</v>
+        <v>2.32</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>42.86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Nestle India Ltd</t>
+          <t>ITC Ltd</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>117.75</v>
+        <v>29.47</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>185.43</v>
+        <v>34.76</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>16.12</v>
+        <v>29.28</v>
       </c>
       <c r="H3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P4" s="9" t="n">
         <v>71.43000000000001</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>0.1033</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>2938</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="3" t="n">
-        <v>41.1862</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>2.3182</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Hindustan Unilever Ltd</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="H4" s="8" t="n">
+      <c r="Q4" s="8" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="I4" s="7" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>10145</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr"/>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="7" t="n">
-        <v>57.847</v>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>0.7886</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>57.14</v>
+      <c r="U4" s="8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd</t>
+          <t>Tata Consumer Products Ltd</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>54.15</v>
+        <v>8.32</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>28.57</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>10.6</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>14.29</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>3050</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+        <v>7.99</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>83.33</v>
+      </c>
       <c r="S5" s="3" t="n">
-        <v>20.5976</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>1.8484</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>85.70999999999999</v>
-      </c>
+        <v>25.32</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Dabur India Ltd</t>
+          <t>Britannia Industries Ltd</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>18.36</v>
+        <v>57.1</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="H6" s="4" t="n">
         <v>42.86</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="I6" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T6" s="4" t="n">
         <v>28.57</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.1384</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>1042</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="3" t="n">
-        <v>23.2419</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>42.86</v>
-      </c>
       <c r="U6" s="3" t="n">
-        <v>0.8206</v>
+        <v>1.85</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>71.43000000000001</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd</t>
+          <t>Dabur India Ltd</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="D7" s="5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>28.57</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>14.29</v>
-      </c>
       <c r="G7" s="3" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H7" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="P7" s="4" t="n">
         <v>28.57</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>0.2165</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>16.67</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>25.3218</v>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>57.14</v>
+        <v>23.24</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>42.86</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.5454</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>14.29</v>
+        <v>0.82</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>66.67</v>
       </c>
     </row>
     <row r="8">
@@ -2878,52 +3078,52 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>14.29</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>26.49</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>42.86</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>-3.98</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="6" t="n">
         <v>14.29</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.2558</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>-1365</v>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>14.29</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="O8" s="3" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>14.29</v>
+      </c>
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>2.4129</v>
-      </c>
-      <c r="T8" s="9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T8" s="6" t="n">
         <v>14.29</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.7664</v>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>28.57</v>
+        <v>0.77</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9"/>
@@ -2935,7 +3135,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="n">
-        <v>20.07</v>
+        <v>20.2</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>57.14</v>
@@ -2953,23 +3153,31 @@
         <v>57.14</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>2938</v>
-      </c>
-      <c r="L10" s="11" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="11" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="P10" s="11" t="n">
         <v>57.14</v>
       </c>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="10" t="n"/>
-      <c r="R10" s="10" t="n"/>
+      <c r="Q10" s="11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="R10" s="11" t="n">
+        <v>58.34</v>
+      </c>
       <c r="S10" s="11" t="n">
         <v>25.32</v>
       </c>
@@ -2977,10 +3185,10 @@
         <v>57.14</v>
       </c>
       <c r="U10" s="11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="V10" s="11" t="n">
-        <v>57.14</v>
+        <v>58.34</v>
       </c>
     </row>
   </sheetData>
@@ -3136,243 +3344,267 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services Ltd</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>0.0886</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>50429</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" s="6" t="inlineStr"/>
-      <c r="N2" s="6" t="inlineStr"/>
-      <c r="O2" s="6" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="7" t="n">
-        <v>87.0951</v>
-      </c>
-      <c r="T2" s="8" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Infosys Ltd</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="U2" s="7" t="n">
-        <v>1.6559</v>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v>100</v>
+      <c r="G2" s="3" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>66.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Infosys Ltd</t>
+          <t>LTIMindtree Ltd</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>29.79</v>
-      </c>
-      <c r="D3" s="4" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>80</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="I3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="R3" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="H3" s="4" t="n">
+      <c r="S3" s="3" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>0.0949</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>20117</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="3" t="n">
-        <v>87.5234</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>1.1298</v>
-      </c>
-      <c r="V3" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>HCL Technologies Ltd</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>23.01</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.0844</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>15840</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="3" t="n">
-        <v>46.4611</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1.1102</v>
-      </c>
-      <c r="V4" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="U4" s="7" t="inlineStr"/>
+      <c r="V4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LTIMindtree Ltd</t>
+          <t>HCL Technologies Ltd</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="D5" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="3" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>40</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>0.1035</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>1752</v>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="3" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="S5" s="3" t="n">
-        <v>31.9324</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>40</v>
+        <v>46.46</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>1.2895</v>
+        <v>1.11</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>80</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="6">
@@ -3387,53 +3619,53 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>20</v>
+        <v>8.630000000000001</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.61</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>0.0951</v>
-      </c>
-      <c r="J6" s="9" t="n">
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="n">
+        <v>-10.99</v>
+      </c>
+      <c r="N6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>5058</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="S6" s="3" t="n">
-        <v>13.8597</v>
-      </c>
-      <c r="T6" s="9" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="T6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>1.205</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>60</v>
-      </c>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
     </row>
     <row r="7"/>
     <row r="8">
@@ -3444,7 +3676,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="n">
-        <v>23.01</v>
+        <v>23.3</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>60</v>
@@ -3465,20 +3697,28 @@
         <v>0.09</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>15840</v>
-      </c>
-      <c r="L8" s="11" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="11" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="10" t="n"/>
+      <c r="O8" s="11" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="S8" s="11" t="n">
         <v>46.46</v>
       </c>
@@ -3486,10 +3726,10 @@
         <v>60</v>
       </c>
       <c r="U8" s="11" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="V8" s="11" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
@@ -3645,62 +3885,66 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>LICI</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Life Insurance Corporation of India</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="7" t="n">
+      <c r="C2" s="8" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>63.79</v>
       </c>
-      <c r="F2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" s="7" t="n">
+      <c r="F2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="8" t="n">
         <v>4.84</v>
       </c>
-      <c r="H2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" s="7" t="n">
+      <c r="H2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="8" t="n">
+      <c r="J2" s="9" t="n">
         <v>62.5</v>
       </c>
-      <c r="K2" s="7" t="n">
-        <v>853</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" s="6" t="inlineStr"/>
-      <c r="N2" s="6" t="inlineStr"/>
-      <c r="O2" s="6" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="7" t="n">
-        <v>371.9375</v>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="U2" s="7" t="n">
-        <v>0.1591</v>
-      </c>
-      <c r="V2" s="8" t="n">
+      <c r="K2" s="7" t="inlineStr"/>
+      <c r="L2" s="7" t="inlineStr"/>
+      <c r="M2" s="8" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="N2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="P2" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="7" t="inlineStr"/>
+      <c r="R2" s="7" t="inlineStr"/>
+      <c r="S2" s="8" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="T2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V2" s="9" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3716,51 +3960,59 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="D3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>75</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>75</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>1.43</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="4" t="n">
         <v>50</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="4" t="n">
         <v>62.5</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>-2099</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="S3" s="3" t="n">
-        <v>240.3333</v>
-      </c>
-      <c r="T3" s="4" t="n">
+        <v>240.33</v>
+      </c>
+      <c r="T3" s="5" t="n">
         <v>75</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.3314</v>
-      </c>
-      <c r="V3" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V3" s="5" t="n">
         <v>75</v>
       </c>
     </row>
@@ -3776,51 +4028,59 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="D4" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>50</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>6.61</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="6" t="n">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>1.55</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>75</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.0648</v>
-      </c>
-      <c r="J4" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>-2893</v>
-      </c>
-      <c r="L4" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>66.67</v>
+      </c>
       <c r="S4" s="3" t="n">
-        <v>192.2895</v>
-      </c>
-      <c r="T4" s="5" t="n">
+        <v>192.29</v>
+      </c>
+      <c r="T4" s="4" t="n">
         <v>50</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.3353</v>
-      </c>
-      <c r="V4" s="4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V4" s="5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3836,51 +4096,59 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="D5" s="9" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>25</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>8.75</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="6" t="n">
         <v>25</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="J5" s="9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="3" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>33.33</v>
+      </c>
       <c r="S5" s="3" t="n">
-        <v>31.0215</v>
-      </c>
-      <c r="T5" s="9" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="T5" s="6" t="n">
         <v>25</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="V5" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V5" s="4" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3893,7 +4161,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="n">
-        <v>11.71</v>
+        <v>11.7</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>62.5</v>
@@ -3916,18 +4184,26 @@
       <c r="J7" s="11" t="n">
         <v>43.75</v>
       </c>
-      <c r="K7" s="11" t="n">
-        <v>-997</v>
-      </c>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="11" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="N7" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="M7" s="10" t="n"/>
-      <c r="N7" s="10" t="n"/>
-      <c r="O7" s="10" t="n"/>
-      <c r="P7" s="10" t="n"/>
-      <c r="Q7" s="10" t="n"/>
-      <c r="R7" s="10" t="n"/>
+      <c r="O7" s="11" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>66.67</v>
+      </c>
       <c r="S7" s="11" t="n">
         <v>216.31</v>
       </c>
@@ -3959,11 +4235,11 @@
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -4096,300 +4372,340 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corpn Ltd</t>
+          <t>Bharat Petroleum Corporation Ltd</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>16.94</v>
+        <v>41.9</v>
       </c>
       <c r="D2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="P2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.4544</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>42060</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="3" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="S2" s="3" t="n">
-        <v>11.3613</v>
+        <v>11.36</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.8332000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd</t>
+          <t>GAIL (India) Ltd</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>35.51000000000001</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>32.1</v>
+        <v>14.7</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>40</v>
+        <v>7.43</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.7219</v>
-      </c>
-      <c r="J3" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="N3" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>25415</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="O3" s="3" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="S3" s="3" t="n">
-        <v>11.3555</v>
+        <v>23.62</v>
       </c>
       <c r="T3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V3" s="4" t="n">
         <v>60</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>2.2137</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd</t>
+          <t>Indian Oil Corporation</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12.86</v>
+        <v>25.44</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="Q4" s="3" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="T4" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>7.430000000000001</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="U4" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V4" s="5" t="n">
         <v>80</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>4360</v>
-      </c>
-      <c r="L4" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="3" t="n">
-        <v>23.6245</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1.0681</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Indian Oil Corporation</t>
+          <t>Oil &amp; Natural Gas Corpn Ltd</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>23.53</v>
+        <v>14.32</v>
       </c>
       <c r="D5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="3" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Reliance Industries Ltd</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="H6" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="I6" s="8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr"/>
+      <c r="M6" s="8" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="P6" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="H5" s="9" t="n">
+      <c r="Q6" s="8" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="R6" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="T6" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>0.7231</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>39635</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="3" t="n">
-        <v>10.2823</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>1.6084</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Reliance Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>8.790000000000001</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.5785</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>45207</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="6" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="7" t="n">
-        <v>7.7289</v>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="U6" s="7" t="n">
-        <v>0.5123</v>
-      </c>
-      <c r="V6" s="8" t="n">
+      <c r="U6" s="8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4402,7 +4718,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="n">
-        <v>16.94</v>
+        <v>14.32</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>60</v>
@@ -4425,23 +4741,31 @@
       <c r="J8" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="K8" s="11" t="n">
-        <v>39635</v>
-      </c>
-      <c r="L8" s="11" t="n">
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="11" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="10" t="n"/>
+      <c r="O8" s="11" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="S8" s="11" t="n">
         <v>11.36</v>
       </c>
       <c r="T8" s="11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="U8" s="11" t="n">
         <v>1.07</v>
@@ -4605,301 +4929,325 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cipla Ltd</t>
+          <t>Dr Reddys Laboratories Ltd</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>15.55</v>
+        <v>21.4</v>
       </c>
       <c r="D2" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="N2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="O2" s="3" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="R2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="H2" s="5" t="n">
+      <c r="S2" s="3" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>66.67</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D3" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="J2" s="5" t="n">
+      <c r="E3" s="8" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H3" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>1152</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="3" t="n">
-        <v>35.3388</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>0.7922</v>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Dr Reddys Laboratories Ltd</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>19.74</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
+      <c r="M3" s="8" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="N3" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="H3" s="4" t="n">
+      <c r="O3" s="8" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="P3" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>0.0709</v>
-      </c>
-      <c r="J3" s="9" t="n">
+      <c r="Q3" s="8" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="R3" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="T3" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="U3" s="7" t="inlineStr"/>
+      <c r="V3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Ltd</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>509</v>
-      </c>
-      <c r="L3" s="9" t="n">
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="P4" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="3" t="n">
-        <v>51.7076</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0.7223000000000001</v>
-      </c>
-      <c r="V3" s="5" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceuticals Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0.0514</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>11372</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr"/>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="7" t="n">
-        <v>58.3319</v>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>0.5685</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="Q4" s="3" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Divis Laboratories Ltd</t>
+          <t>Cipla Ltd</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>20</v>
+        <v>16.8</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>20</v>
+        <v>22.8</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>20.4</v>
+        <v>16.12</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.0002</v>
+        <v>0.02</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>992</v>
-      </c>
-      <c r="L5" s="5" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="3" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+      <c r="O5" s="3" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>40</v>
+      </c>
       <c r="S5" s="3" t="n">
-        <v>636.25</v>
+        <v>35.34</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.5074</v>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v>20</v>
+        <v>0.79</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd</t>
+          <t>Divis Laboratories Ltd</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>100</v>
+        <v>12.2</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>80</v>
+        <v>16.5</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="H6" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>0.5866</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>3106</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="S6" s="3" t="n">
-        <v>9.926600000000001</v>
-      </c>
-      <c r="T6" s="9" t="n">
-        <v>20</v>
+        <v>636.25</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.7396</v>
+        <v>0.51</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>80</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="7"/>
@@ -4911,7 +5259,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="n">
-        <v>15.55</v>
+        <v>16.8</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>60</v>
@@ -4929,23 +5277,31 @@
         <v>60</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>1152</v>
-      </c>
-      <c r="L8" s="11" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="11" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="10" t="n"/>
+      <c r="O8" s="11" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="S8" s="11" t="n">
         <v>51.71</v>
       </c>
@@ -4956,7 +5312,7 @@
         <v>0.72</v>
       </c>
       <c r="V8" s="11" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
@@ -5123,51 +5479,55 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="D2" s="4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>85.70999999999999</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>41.37</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>85.70999999999999</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.8023</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>83.33</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>17651</v>
       </c>
-      <c r="L2" s="4" t="n">
-        <v>85.70999999999999</v>
+      <c r="L2" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="O2" s="3" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>85.70999999999999</v>
+      </c>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="3" t="n">
-        <v>8.2972</v>
-      </c>
-      <c r="T2" s="4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="T2" s="5" t="n">
         <v>85.70999999999999</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.5472</v>
-      </c>
-      <c r="V2" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="V2" s="5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -5183,352 +5543,388 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="D3" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>85.70999999999999</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="4" t="n">
         <v>71.43000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>33.97</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="4" t="n">
         <v>71.43000000000001</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1.4173</v>
-      </c>
-      <c r="J3" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>NTPC Ltd</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="D4" s="9" t="n">
         <v>57.14</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>24176</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="3" t="n">
-        <v>4.603</v>
-      </c>
-      <c r="T3" s="5" t="n">
+      <c r="E4" s="8" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="P4" s="9" t="n">
         <v>57.14</v>
       </c>
-      <c r="U3" s="3" t="n">
-        <v>0.1828</v>
-      </c>
-      <c r="V3" s="5" t="n">
-        <v>42.86</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>NTPC Ltd</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>1.4755</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>8644</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr"/>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="7" t="n">
-        <v>4.605</v>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>0.3724</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>71.43000000000001</v>
+      <c r="Q4" s="8" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T4" s="9" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v>83.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>NHPC Ltd</t>
+          <t>Adani Green Energy Ltd</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>28.57</v>
+        <v>14.7</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>71.43000000000001</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>14.29</v>
+        <v>96.5</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>41.82</v>
+        <v>13.67</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>100</v>
+        <v>42.86</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.8413</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>71.43000000000001</v>
+        <v>6.6</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>970</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>42.86</v>
+        <v>-13347</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="O5" s="3" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>11.2434</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>100</v>
+        <v>1.71</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>14.29</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.1032</v>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v>14.29</v>
+        <v>0.1</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tata Power Company Ltd</t>
+          <t>JSW Energy Ltd</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="D6" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="H6" s="4" t="n">
         <v>57.14</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>14.29</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>1.6593</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>3569</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+        <v>1.52</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="S6" s="3" t="n">
-        <v>3.0544</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>42.86</v>
+        <v>2.85</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>28.57</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.4419</v>
+        <v>0.2</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd</t>
+          <t>Tata Power Company Ltd</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="D7" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>42.86</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>96.5</v>
+        <v>11.1</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>100</v>
+        <v>57.14</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="H7" s="5" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="3" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T7" s="4" t="n">
         <v>42.86</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>6.5953</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>-13347</v>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="3" t="n">
-        <v>1.7139</v>
-      </c>
-      <c r="T7" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0.1047</v>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>28.57</v>
-      </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>JSW Energy Ltd</t>
+          <t>NHPC Ltd</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>14.29</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>28.57</v>
-      </c>
       <c r="G8" s="3" t="n">
-        <v>15.02</v>
+        <v>41.82</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>57.14</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.5156</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>-1963</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="S8" s="3" t="n">
-        <v>2.8514</v>
+        <v>11.24</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>28.57</v>
+        <v>100</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.1988</v>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>57.14</v>
+        <v>0.1</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9"/>
@@ -5540,7 +5936,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="n">
-        <v>13.23</v>
+        <v>12.52</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>57.14</v>
@@ -5558,34 +5954,46 @@
         <v>57.14</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>42.86</v>
+        <v>41.66</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>3569</v>
+        <v>2152</v>
       </c>
       <c r="L10" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="P10" s="11" t="n">
         <v>57.14</v>
       </c>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="10" t="n"/>
-      <c r="R10" s="10" t="n"/>
+      <c r="Q10" s="11" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="R10" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="S10" s="11" t="n">
         <v>4.6</v>
       </c>
       <c r="T10" s="11" t="n">
-        <v>57.14</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="U10" s="11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="V10" s="11" t="n">
-        <v>57.14</v>
+        <v>58.34</v>
       </c>
     </row>
   </sheetData>
@@ -5743,301 +6151,341 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd</t>
+          <t>ICICI Bank Ltd</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="D2" s="9" t="n">
-        <v>20</v>
+        <v>18.8</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7.86</v>
+        <v>7.6</v>
       </c>
       <c r="F2" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>100</v>
-      </c>
       <c r="I2" s="3" t="n">
-        <v>4.0037</v>
+        <v>6.45</v>
       </c>
       <c r="J2" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="P2" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>6766</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="3" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="S2" s="3" t="n">
-        <v>1.2364</v>
-      </c>
-      <c r="T2" s="9" t="n">
-        <v>20</v>
+        <v>1.3</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.0733</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd</t>
+          <t>IndusInd Bank Ltd</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>17.99</v>
+        <v>15.2</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7.6</v>
+        <v>7.93</v>
       </c>
       <c r="F3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="N3" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>28.89</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>6.4456</v>
-      </c>
-      <c r="J3" s="5" t="n">
+      <c r="O3" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>12547</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="Q3" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>40</v>
+      </c>
       <c r="S3" s="3" t="n">
-        <v>1.3009</v>
+        <v>1.88</v>
       </c>
       <c r="T3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="J4" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="U3" s="3" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="V3" s="9" t="n">
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="R4" s="9" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>HDFC Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="D4" s="8" t="n">
+      <c r="S4" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>23.07</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>6.8088</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>35669</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr"/>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="7" t="n">
-        <v>1.4008</v>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>0.0704</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>40</v>
+      <c r="U4" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd</t>
+          <t>Axis Bank Ltd</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>14.25</v>
+        <v>18.4</v>
       </c>
       <c r="D5" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>20</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>6.8857</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>-17468</v>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+        <v>8.25</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="3" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>80</v>
+      </c>
       <c r="S5" s="3" t="n">
-        <v>1.8795</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>100</v>
+        <v>1.69</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>80</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.0888</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd</t>
+          <t>Kotak Mahindra Bank Ltd</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="D6" s="4" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="F6" s="9" t="n">
+      <c r="G6" s="3" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="N6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>22.73</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>8.2491</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-14556</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="S6" s="3" t="n">
-        <v>1.6912</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>80</v>
+        <v>1.24</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>60</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="7"/>
@@ -6049,7 +6497,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="n">
-        <v>14.34</v>
+        <v>17.1</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>60</v>
@@ -6072,18 +6520,26 @@
       <c r="J8" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="K8" s="11" t="n">
-        <v>6766</v>
-      </c>
-      <c r="L8" s="11" t="n">
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="11" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="10" t="n"/>
+      <c r="O8" s="11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="S8" s="11" t="n">
         <v>1.4</v>
       </c>
@@ -6094,7 +6550,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="V8" s="11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
